--- a/library.xlsx
+++ b/library.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F472"/>
+  <dimension ref="A1:F499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,10 +1363,10 @@
         <v>46041.62687697916</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         <v>46049.56071256944</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3547,10 +3547,10 @@
         <v>46049.66902344907</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3755,10 +3755,10 @@
         <v>46050.60422060185</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>46054.92412278935</v>
       </c>
       <c r="D174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>46116</v>
+        <v>46132</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
         <v>46055.90292584491</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -5965,10 +5965,10 @@
         <v>46061.27357231481</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         <v>46066</v>
       </c>
       <c r="D272" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -8123,10 +8123,10 @@
         <v>46079</v>
       </c>
       <c r="D296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>46117</v>
+        <v>46125</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -8305,10 +8305,10 @@
         <v>46080</v>
       </c>
       <c r="D303" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>46116</v>
+        <v>46148</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         <v>46084</v>
       </c>
       <c r="D304" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>46116</v>
+        <v>46148</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -8357,10 +8357,10 @@
         <v>46084</v>
       </c>
       <c r="D305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>46116</v>
+        <v>46148</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -8409,10 +8409,10 @@
         <v>46084</v>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>46116</v>
+        <v>46132</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>46084</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -8539,10 +8539,10 @@
         <v>46084</v>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         <v>46084</v>
       </c>
       <c r="D322" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>46116</v>
+        <v>46148</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -8929,10 +8929,10 @@
         <v>46085</v>
       </c>
       <c r="D327" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -9007,10 +9007,10 @@
         <v>46085</v>
       </c>
       <c r="D330" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>46116</v>
+        <v>46148</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -9059,10 +9059,10 @@
         <v>46085</v>
       </c>
       <c r="D332" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>46116</v>
+        <v>46132</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>46085</v>
       </c>
       <c r="D333" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>46116</v>
+        <v>46148</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -9163,10 +9163,10 @@
         <v>46087</v>
       </c>
       <c r="D336" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -9709,10 +9709,10 @@
         <v>46089</v>
       </c>
       <c r="D357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E357" s="2" t="n">
-        <v>46116</v>
+        <v>46120</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -9969,10 +9969,10 @@
         <v>46092</v>
       </c>
       <c r="D367" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E367" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -10463,10 +10463,10 @@
         <v>46095</v>
       </c>
       <c r="D386" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E386" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -10489,10 +10489,10 @@
         <v>46095</v>
       </c>
       <c r="D387" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E387" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -10645,10 +10645,10 @@
         <v>46095</v>
       </c>
       <c r="D393" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E393" s="2" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -10775,10 +10775,10 @@
         <v>46097</v>
       </c>
       <c r="D398" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E398" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -11919,10 +11919,10 @@
         <v>46107</v>
       </c>
       <c r="D442" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E442" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -12127,10 +12127,10 @@
         <v>46108</v>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E450" s="2" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -12153,10 +12153,10 @@
         <v>46108</v>
       </c>
       <c r="D451" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E451" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -12179,10 +12179,10 @@
         <v>46108</v>
       </c>
       <c r="D452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E452" s="2" t="n">
-        <v>46116</v>
+        <v>46124</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -12283,10 +12283,10 @@
         <v>46108</v>
       </c>
       <c r="D456" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E456" s="2" t="n">
-        <v>46117</v>
+        <v>46125</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         <v>46108</v>
       </c>
       <c r="D459" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E459" s="2" t="n">
-        <v>46117</v>
+        <v>46125</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -12387,10 +12387,10 @@
         <v>46108</v>
       </c>
       <c r="D460" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E460" s="2" t="n">
-        <v>46116</v>
+        <v>46124</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -12401,246 +12401,246 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>我一般七天起床</t>
+          <t>学期</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Tôi thường dậy lúc 7 giờ</t>
+          <t>học kỳ</t>
         </is>
       </c>
       <c r="C461" s="2" t="n">
         <v>46110</v>
       </c>
       <c r="D461" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E461" s="2" t="n">
-        <v>46117</v>
+        <v>46125</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>wǒ yì bān qī tiān qǐ chuáng</t>
+          <t>xué qī</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>学期</t>
+          <t>我喜欢这种颜色</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>học kỳ</t>
+          <t>Tôi thích màu này</t>
         </is>
       </c>
       <c r="C462" s="2" t="n">
         <v>46110</v>
       </c>
       <c r="D462" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E462" s="2" t="n">
-        <v>46117</v>
+        <v>46125</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>xué qī</t>
+          <t>wǒ xǐ huān zhè zhǒng yán sè</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>我喜欢这种颜色</t>
+          <t>太阳</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Tôi thích màu này</t>
+          <t>mặt trời</t>
         </is>
       </c>
       <c r="C463" s="2" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="D463" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E463" s="2" t="n">
-        <v>46117</v>
+        <v>46126</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>wǒ xǐ huān zhè zhǒng yán sè</t>
+          <t>tài yáng</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>太阳</t>
+          <t>别生气</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>mặt trời</t>
+          <t>Đừng tức giận</t>
         </is>
       </c>
       <c r="C464" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="D464" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E464" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>tài yáng</t>
+          <t>bié shēng qì</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>别生气</t>
+          <t>行李箱</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Đừng tức giận</t>
+          <t>hành lí, vali</t>
         </is>
       </c>
       <c r="C465" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="D465" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E465" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>bié shēng qì</t>
+          <t>xíng lǐ xiāng</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>行李箱</t>
+          <t>我自己做饭</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>hành lí, vali</t>
+          <t>Tôi tự nấu ăn</t>
         </is>
       </c>
       <c r="C466" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="D466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E466" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>xíng lǐ xiāng</t>
+          <t>wǒ zì jǐ zuò fàn</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>我自己做饭</t>
+          <t>她发现这个问题特别重要</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Tôi tự nấu ăn</t>
+          <t>Cô ấy nhận ra vấn đề này đặc biệt quan trọng</t>
         </is>
       </c>
       <c r="C467" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="D467" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E467" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>wǒ zì jǐ zuò fàn</t>
+          <t>tā fā xiàn zhè ge wèn tí tè bié zhòng yào</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>她发现这个问题特别重要</t>
+          <t>出国需要护照</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Cô ấy nhận ra vấn đề này đặc biệt quan trọng</t>
+          <t>Đi nước ngoài cần hộ chiếu</t>
         </is>
       </c>
       <c r="C468" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="D468" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E468" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>tā fā xiàn zhè ge wèn tí tè bié zhòng yào</t>
+          <t>chū guó xū yào hù zhào</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>出国需要护照</t>
+          <t>飞机八点才起飞</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Đi nước ngoài cần hộ chiếu</t>
+          <t>Máy bay đến 8 giờ mới cất cánh</t>
         </is>
       </c>
       <c r="C469" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="D469" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E469" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>chū guó xū yào hù zhào</t>
+          <t>fēi jī bā diǎn cái qǐ fēi</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>飞机八点才起飞</t>
+          <t>他是一个司机</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Máy bay đến 8 giờ mới cất cánh</t>
+          <t>Anh ấy là một tài xế</t>
         </is>
       </c>
       <c r="C470" s="2" t="n">
@@ -12650,23 +12650,23 @@
         <v>3</v>
       </c>
       <c r="E470" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>fēi jī bā diǎn cái qǐ fēi</t>
+          <t>tā shì yí gè sī jī</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>他是一个司机</t>
+          <t>黑板</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Anh ấy là một tài xế</t>
+          <t>bảng đen, bảng viết</t>
         </is>
       </c>
       <c r="C471" s="2" t="n">
@@ -12676,37 +12676,739 @@
         <v>3</v>
       </c>
       <c r="E471" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>tā shì yí gè sī jī</t>
+          <t>hēi bǎn</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>黑板</t>
+          <t>她终于来了</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>bảng đen, bảng viết</t>
+          <t>Cuối cùng cô ấy cũng đến rồi</t>
         </is>
       </c>
       <c r="C472" s="2" t="n">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="D472" t="n">
+        <v>3</v>
+      </c>
+      <c r="E472" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>tā zhōng yú lái le</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>我在工作中遇到很多困难</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Tôi gặp rất nhiều khó khăn trong công việc</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D473" t="n">
+        <v>3</v>
+      </c>
+      <c r="E473" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>wǒ zài gōng zuò zhōng yù dào hěn duō kùn nán</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>我们应该忘记过去</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Chúng ta nên quên quá khứ</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D474" t="n">
         <v>2</v>
       </c>
-      <c r="E472" s="2" t="n">
+      <c r="E474" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>wǒ men yīng gāi wàng jì guò qù</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>冬天已经过去了</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Mùa đông đã qua rồi</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D475" t="n">
+        <v>3</v>
+      </c>
+      <c r="E475" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>dōng tiān yǐ jīng guò qù le</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>我很愿意参加这个活动</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Tôi rất sẵn lòng tham gia hoạt động này</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D476" t="n">
+        <v>1</v>
+      </c>
+      <c r="E476" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>wǒ hěn yuàn yì cān jiā zhè ge huó dòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>她马上站起来</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Cô ấy lập tức đứng dậy</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D477" t="n">
+        <v>3</v>
+      </c>
+      <c r="E477" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>tā mǎ shàng zhàn qǐ lái</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>她说的话听起来很有道理</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Lời cô ấy nghe có lý</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D478" t="n">
+        <v>3</v>
+      </c>
+      <c r="E478" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>tā shuō de huà tīng qǐ lái hěn yǒu dào lǐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>我的生活很简单</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Cuộc sống của tôi rất đơn giản</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D479" t="n">
+        <v>3</v>
+      </c>
+      <c r="E479" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>wǒ de shēng huó hěn jiǎn dān</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>我们的校长很严格</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng của chúng tôi rất nghiêm khắc</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D480" t="n">
+        <v>2</v>
+      </c>
+      <c r="E480" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>wǒ men de xiào zhǎng hěn yán gé</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>今天的天气很坏</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Thời tiết hôm nay rất xấu</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D481" t="n">
+        <v>3</v>
+      </c>
+      <c r="E481" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>jīn tiān de tiān qì hěn huài</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>电脑又坏了</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Máy tính lại hỏng rồi</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D482" t="n">
+        <v>3</v>
+      </c>
+      <c r="E482" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>diàn nǎo yòu huài le</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>菜单</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>thực đơn</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>hēi bǎn</t>
+      <c r="D483" t="n">
+        <v>3</v>
+      </c>
+      <c r="E483" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>cài dān</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>盘子</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>đĩa, mâm</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D484" t="n">
+        <v>3</v>
+      </c>
+      <c r="E484" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>pán zi</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>节目</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>chương trình</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D485" t="n">
+        <v>3</v>
+      </c>
+      <c r="E485" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>jié mù</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>月亮</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>mặt trăng</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D486" t="n">
+        <v>3</v>
+      </c>
+      <c r="E486" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>yuè liàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>刷牙</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>đánh răng</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D487" t="n">
+        <v>3</v>
+      </c>
+      <c r="E487" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>shuā yá</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>洗脸</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>rửa mặt</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D488" t="n">
+        <v>3</v>
+      </c>
+      <c r="E488" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>xǐ liǎn</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>她洗了澡， 然后睡觉</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Cô ấy tắm xong rồi đi ngủ</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D489" t="n">
+        <v>3</v>
+      </c>
+      <c r="E489" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>tā xǐ le zǎo ，  rán hòu shuì jiào</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>她像她妈妈一样</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Cô ấy giống mẹ cô ấy</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D490" t="n">
+        <v>3</v>
+      </c>
+      <c r="E490" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>tā xiàng tā mā mā yī yàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>外面刮风了</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Bên ngoài có gió</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D491" t="n">
+        <v>3</v>
+      </c>
+      <c r="E491" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>wài miàn guā fēng le</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>叔叔</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>chú</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D492" t="n">
+        <v>3</v>
+      </c>
+      <c r="E492" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>shū shū</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>阿姨</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>cô, dì</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D493" t="n">
+        <v>3</v>
+      </c>
+      <c r="E493" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>ā yí</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>外面有奇怪的声音</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Bên ngoài có âm thanh lạ</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D494" t="n">
+        <v>2</v>
+      </c>
+      <c r="E494" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>wài miàn yǒu qí guài de shēng yīn</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>她说得很简单</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Cô ấy nói rất dễ hiểu</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D495" t="n">
+        <v>3</v>
+      </c>
+      <c r="E495" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>tā shuō dé hěn jiǎn dān</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>请把这本书拿过去</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Hãy mang quyển sách này qua đó</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D496" t="n">
+        <v>3</v>
+      </c>
+      <c r="E496" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>qǐng bǎ zhè běn shū ná guò qù</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>我把房间打扫得很干净</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Tôi dọn phòng rất sạch</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D497" t="n">
+        <v>2</v>
+      </c>
+      <c r="E497" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>wǒ bǎ fáng jiān dǎ sǎo dé hěn gān jìng</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>我一般七点起床</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Tôi thường dậy lúc 7 giờ</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D498" t="n">
+        <v>2</v>
+      </c>
+      <c r="E498" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>wǒ yì bān qī diǎn qǐ chuáng</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>她忙坏了</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Cô ấy bận điêng :)))</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D499" t="n">
+        <v>1</v>
+      </c>
+      <c r="E499" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>tā máng huái le</t>
         </is>
       </c>
     </row>
